--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_araucania.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_araucania.xlsx
@@ -404,7 +404,7 @@
         <v>26.16275404047834</v>
       </c>
       <c r="D2">
-        <v>1.742112055945592</v>
+        <v>3.201143722142797</v>
       </c>
       <c r="E2">
         <v>19.84658163452648</v>
@@ -429,7 +429,7 @@
         <v>27.90524618628302</v>
       </c>
       <c r="D3">
-        <v>1.452661922349338</v>
+        <v>2.442963187395849</v>
       </c>
       <c r="E3">
         <v>24.24431630366916</v>
@@ -454,7 +454,7 @@
         <v>28.77290769360696</v>
       </c>
       <c r="D4">
-        <v>1.305512679162073</v>
+        <v>2.090941197245276</v>
       </c>
       <c r="E4">
         <v>27.08144039022524</v>
@@ -479,7 +479,7 @@
         <v>30.88959212376934</v>
       </c>
       <c r="D5">
-        <v>1.501583949313622</v>
+        <v>2.800590841949778</v>
       </c>
       <c r="E5">
         <v>21.43309413254538</v>
@@ -504,7 +504,7 @@
         <v>24.54930148976871</v>
       </c>
       <c r="D6">
-        <v>1.531380381713271</v>
+        <v>2.453911806543386</v>
       </c>
       <c r="E6">
         <v>24.65282648337775</v>
@@ -529,7 +529,7 @@
         <v>27.70131136880893</v>
       </c>
       <c r="D7">
-        <v>1.575110959371799</v>
+        <v>2.794367050272562</v>
       </c>
       <c r="E7">
         <v>21.88929400066291</v>
@@ -554,7 +554,7 @@
         <v>28.57635298173043</v>
       </c>
       <c r="D8">
-        <v>1.30832832230908</v>
+        <v>2.089555822328931</v>
       </c>
       <c r="E8">
         <v>27.12471507652231</v>
@@ -579,7 +579,7 @@
         <v>29.23181024965277</v>
       </c>
       <c r="D9">
-        <v>1.625036171074715</v>
+        <v>3.095469077279242</v>
       </c>
       <c r="E9">
         <v>19.99867719035231</v>
@@ -604,7 +604,7 @@
         <v>27.33910055831646</v>
       </c>
       <c r="D10">
-        <v>1.434771126760564</v>
+        <v>2.360805330243337</v>
       </c>
       <c r="E10">
         <v>24.96113380816371</v>
@@ -629,7 +629,7 @@
         <v>26.670692431562</v>
       </c>
       <c r="D11">
-        <v>1.400620242458416</v>
+        <v>2.235823582358236</v>
       </c>
       <c r="E11">
         <v>26.095126247798</v>
@@ -654,7 +654,7 @@
         <v>29.14494741655235</v>
       </c>
       <c r="D12">
-        <v>1.437680778332895</v>
+        <v>2.474541751527495</v>
       </c>
       <c r="E12">
         <v>23.83366592956151</v>
@@ -679,7 +679,7 @@
         <v>29.11795761369635</v>
       </c>
       <c r="D13">
-        <v>1.675861851044333</v>
+        <v>3.273019007652432</v>
       </c>
       <c r="E13">
         <v>19.13489130049715</v>
@@ -704,7 +704,7 @@
         <v>28.7337326998554</v>
       </c>
       <c r="D14">
-        <v>1.499690210656753</v>
+        <v>2.635274904735982</v>
       </c>
       <c r="E14">
         <v>22.76614202503408</v>
@@ -729,7 +729,7 @@
         <v>27.42812307347419</v>
       </c>
       <c r="D15">
-        <v>1.46735197368421</v>
+        <v>2.455684007707129</v>
       </c>
       <c r="E15">
         <v>24.21757824217578</v>
@@ -754,7 +754,7 @@
         <v>27.27272727272727</v>
       </c>
       <c r="D16">
-        <v>1.757990867579909</v>
+        <v>3.37719298245614</v>
       </c>
       <c r="E16">
         <v>18.87417218543046</v>
@@ -779,7 +779,7 @@
         <v>31.14633247327682</v>
       </c>
       <c r="D17">
-        <v>1.314650298820869</v>
+        <v>2.226203501094092</v>
       </c>
       <c r="E17">
         <v>25.51290997906489</v>
@@ -804,7 +804,7 @@
         <v>27.13747464013139</v>
       </c>
       <c r="D18">
-        <v>1.382345085470086</v>
+        <v>2.212224834366318</v>
       </c>
       <c r="E18">
         <v>26.22904871349291</v>
@@ -829,7 +829,7 @@
         <v>27.01906681134708</v>
       </c>
       <c r="D19">
-        <v>1.398136107498916</v>
+        <v>2.24695228143504</v>
       </c>
       <c r="E19">
         <v>25.9466787166742</v>
@@ -854,7 +854,7 @@
         <v>27.27866405448269</v>
       </c>
       <c r="D20">
-        <v>1.676546492531477</v>
+        <v>3.089494163424125</v>
       </c>
       <c r="E20">
         <v>20.27465303140979</v>
@@ -879,7 +879,7 @@
         <v>29.91024175451967</v>
       </c>
       <c r="D21">
-        <v>1.558958450216165</v>
+        <v>2.920974523868415</v>
       </c>
       <c r="E21">
         <v>20.85660119423774</v>
@@ -904,7 +904,7 @@
         <v>31.9977233921457</v>
       </c>
       <c r="D22">
-        <v>1.496337932209164</v>
+        <v>2.870915032679739</v>
       </c>
       <c r="E22">
         <v>20.87882096069869</v>
@@ -929,7 +929,7 @@
         <v>27.7567281439795</v>
       </c>
       <c r="D23">
-        <v>1.552441503395182</v>
+        <v>2.727922176622587</v>
       </c>
       <c r="E23">
         <v>22.29602643395747</v>
@@ -954,7 +954,7 @@
         <v>27.88311912858049</v>
       </c>
       <c r="D24">
-        <v>1.579661325564457</v>
+        <v>2.823136999674585</v>
       </c>
       <c r="E24">
         <v>21.69048879477678</v>
@@ -979,7 +979,7 @@
         <v>28.08350730688936</v>
       </c>
       <c r="D25">
-        <v>1.331147176522899</v>
+        <v>2.125865435824605</v>
       </c>
       <c r="E25">
         <v>26.86090315197177</v>
@@ -1004,7 +1004,7 @@
         <v>36.51537884471118</v>
       </c>
       <c r="D26">
-        <v>1.404266526204899</v>
+        <v>2.882162162162162</v>
       </c>
       <c r="E26">
         <v>20.26508927593384</v>
@@ -1029,7 +1029,7 @@
         <v>31.65236051502146</v>
       </c>
       <c r="D27">
-        <v>1.498392282958199</v>
+        <v>2.850152905198777</v>
       </c>
       <c r="E27">
         <v>21.04247104247104</v>
@@ -1054,7 +1054,7 @@
         <v>28.71547566856642</v>
       </c>
       <c r="D28">
-        <v>1.406722170829479</v>
+        <v>2.360062079668908</v>
       </c>
       <c r="E28">
         <v>24.76617552850736</v>
@@ -1079,7 +1079,7 @@
         <v>28.90896455872133</v>
       </c>
       <c r="D29">
-        <v>1.44152266466316</v>
+        <v>2.471446972949764</v>
       </c>
       <c r="E29">
         <v>23.88962970561083</v>
@@ -1104,7 +1104,7 @@
         <v>27.81740370898716</v>
       </c>
       <c r="D30">
-        <v>1.483336272262388</v>
+        <v>2.525367757430201</v>
       </c>
       <c r="E30">
         <v>23.65263083149897</v>
@@ -1129,7 +1129,7 @@
         <v>27.25888324873096</v>
       </c>
       <c r="D31">
-        <v>1.611781550419309</v>
+        <v>2.874863188617293</v>
       </c>
       <c r="E31">
         <v>21.46605059127575</v>
@@ -1154,7 +1154,7 @@
         <v>30.4264374530585</v>
       </c>
       <c r="D32">
-        <v>1.312198861147613</v>
+        <v>2.184287276704338</v>
       </c>
       <c r="E32">
         <v>25.9815297182098</v>
@@ -1179,7 +1179,7 @@
         <v>28.74187037452344</v>
       </c>
       <c r="D33">
-        <v>1.427336747759283</v>
+        <v>2.420212765957447</v>
       </c>
       <c r="E33">
         <v>24.29645259132269</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_araucania.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_araucania.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.16275404047834</v>
+      </c>
+      <c r="C2">
         <v>31.2388348290284</v>
-      </c>
-      <c r="C2">
-        <v>26.16275404047834</v>
       </c>
       <c r="D2">
         <v>3.201143722142797</v>
       </c>
       <c r="E2">
-        <v>19.84658163452648</v>
+        <v>16.62165816011456</v>
       </c>
       <c r="F2">
         <v>63.53176020535896</v>
       </c>
       <c r="G2">
-        <v>16.62165816011456</v>
+        <v>19.84658163452648</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.90524618628302</v>
+      </c>
+      <c r="C3">
         <v>40.9338955723676</v>
-      </c>
-      <c r="C3">
-        <v>27.90524618628302</v>
       </c>
       <c r="D3">
         <v>2.442963187395849</v>
       </c>
       <c r="E3">
-        <v>24.24431630366916</v>
+        <v>16.52771146288611</v>
       </c>
       <c r="F3">
         <v>59.22797223344475</v>
       </c>
       <c r="G3">
-        <v>16.52771146288611</v>
+        <v>24.24431630366916</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.77290769360696</v>
+      </c>
+      <c r="C4">
         <v>47.82535258846381</v>
-      </c>
-      <c r="C4">
-        <v>28.77290769360696</v>
       </c>
       <c r="D4">
         <v>2.090941197245276</v>
       </c>
       <c r="E4">
-        <v>27.08144039022524</v>
+        <v>16.29286021711061</v>
       </c>
       <c r="F4">
         <v>56.62569939266415</v>
       </c>
       <c r="G4">
-        <v>16.29286021711061</v>
+        <v>27.08144039022524</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>30.88959212376934</v>
+      </c>
+      <c r="C5">
         <v>35.70675105485232</v>
-      </c>
-      <c r="C5">
-        <v>30.88959212376934</v>
       </c>
       <c r="D5">
         <v>2.800590841949778</v>
       </c>
       <c r="E5">
-        <v>21.43309413254538</v>
+        <v>18.54157872520051</v>
       </c>
       <c r="F5">
-        <v>60.02532714225412</v>
+        <v>60.02532714225411</v>
       </c>
       <c r="G5">
-        <v>18.54157872520051</v>
+        <v>21.43309413254537</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>24.54930148976871</v>
+      </c>
+      <c r="C6">
         <v>40.75126079647557</v>
-      </c>
-      <c r="C6">
-        <v>24.54930148976871</v>
       </c>
       <c r="D6">
         <v>2.453911806543386</v>
       </c>
       <c r="E6">
-        <v>24.65282648337775</v>
+        <v>14.85131154439613</v>
       </c>
       <c r="F6">
         <v>60.49586197222612</v>
       </c>
       <c r="G6">
-        <v>14.85131154439613</v>
+        <v>24.65282648337775</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.70131136880893</v>
+      </c>
+      <c r="C7">
         <v>35.78627939742061</v>
-      </c>
-      <c r="C7">
-        <v>27.70131136880893</v>
       </c>
       <c r="D7">
         <v>2.794367050272562</v>
       </c>
       <c r="E7">
-        <v>21.88929400066291</v>
+        <v>16.94398409015578</v>
       </c>
       <c r="F7">
         <v>61.16672190918131</v>
       </c>
       <c r="G7">
-        <v>16.94398409015578</v>
+        <v>21.88929400066291</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.57635298173043</v>
+      </c>
+      <c r="C8">
         <v>47.85706078363783</v>
-      </c>
-      <c r="C8">
-        <v>28.57635298173043</v>
       </c>
       <c r="D8">
         <v>2.089555822328931</v>
       </c>
       <c r="E8">
-        <v>27.12471507652231</v>
+        <v>16.19667860631716</v>
       </c>
       <c r="F8">
         <v>56.67860631716054</v>
       </c>
       <c r="G8">
-        <v>16.19667860631716</v>
+        <v>27.12471507652231</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>29.23181024965277</v>
+      </c>
+      <c r="C9">
         <v>32.30528152711991</v>
-      </c>
-      <c r="C9">
-        <v>29.23181024965277</v>
       </c>
       <c r="D9">
         <v>3.095469077279242</v>
       </c>
       <c r="E9">
-        <v>19.99867719035231</v>
+        <v>18.09603598042242</v>
       </c>
       <c r="F9">
         <v>61.90528682922528</v>
       </c>
       <c r="G9">
-        <v>18.09603598042242</v>
+        <v>19.99867719035231</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.33910055831646</v>
+      </c>
+      <c r="C10">
         <v>42.35842689735566</v>
-      </c>
-      <c r="C10">
-        <v>27.33910055831646</v>
       </c>
       <c r="D10">
         <v>2.360805330243337</v>
       </c>
       <c r="E10">
-        <v>24.96113380816371</v>
+        <v>16.11048844860624</v>
       </c>
       <c r="F10">
         <v>58.92837774323006</v>
       </c>
       <c r="G10">
-        <v>16.11048844860624</v>
+        <v>24.96113380816371</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.670692431562</v>
+      </c>
+      <c r="C11">
         <v>44.72624798711755</v>
-      </c>
-      <c r="C11">
-        <v>26.670692431562</v>
       </c>
       <c r="D11">
         <v>2.235823582358236</v>
       </c>
       <c r="E11">
-        <v>26.095126247798</v>
+        <v>15.56077510275984</v>
       </c>
       <c r="F11">
         <v>58.34409864944216</v>
       </c>
       <c r="G11">
-        <v>15.56077510275984</v>
+        <v>26.095126247798</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.14494741655235</v>
+      </c>
+      <c r="C12">
         <v>40.41152263374486</v>
-      </c>
-      <c r="C12">
-        <v>29.14494741655235</v>
       </c>
       <c r="D12">
         <v>2.474541751527495</v>
       </c>
       <c r="E12">
-        <v>23.83366592956151</v>
+        <v>17.18893263578016</v>
       </c>
       <c r="F12">
         <v>58.97740143465833</v>
       </c>
       <c r="G12">
-        <v>17.18893263578016</v>
+        <v>23.83366592956151</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>29.11795761369635</v>
+      </c>
+      <c r="C13">
         <v>30.55283203861528</v>
-      </c>
-      <c r="C13">
-        <v>29.11795761369635</v>
       </c>
       <c r="D13">
         <v>3.273019007652432</v>
       </c>
       <c r="E13">
+        <v>18.23624576361253</v>
+      </c>
+      <c r="F13">
+        <v>62.62886293589033</v>
+      </c>
+      <c r="G13">
         <v>19.13489130049715</v>
-      </c>
-      <c r="F13">
-        <v>62.62886293589032</v>
-      </c>
-      <c r="G13">
-        <v>18.23624576361253</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>28.7337326998554</v>
+      </c>
+      <c r="C14">
         <v>37.94670522619293</v>
-      </c>
-      <c r="C14">
-        <v>28.7337326998554</v>
       </c>
       <c r="D14">
         <v>2.635274904735982</v>
       </c>
       <c r="E14">
-        <v>22.76614202503408</v>
+        <v>17.23881521873838</v>
       </c>
       <c r="F14">
         <v>59.99504275622753</v>
       </c>
       <c r="G14">
-        <v>17.23881521873838</v>
+        <v>22.76614202503408</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.42812307347419</v>
+      </c>
+      <c r="C15">
         <v>40.72185170655159</v>
-      </c>
-      <c r="C15">
-        <v>27.42812307347419</v>
       </c>
       <c r="D15">
         <v>2.455684007707129</v>
       </c>
       <c r="E15">
-        <v>24.21757824217578</v>
+        <v>16.31170216311702</v>
       </c>
       <c r="F15">
         <v>59.47071959470719</v>
       </c>
       <c r="G15">
-        <v>16.31170216311702</v>
+        <v>24.21757824217578</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="C16">
         <v>29.61038961038961</v>
-      </c>
-      <c r="C16">
-        <v>27.27272727272727</v>
       </c>
       <c r="D16">
         <v>3.37719298245614</v>
       </c>
       <c r="E16">
-        <v>18.87417218543046</v>
+        <v>17.3841059602649</v>
       </c>
       <c r="F16">
         <v>63.74172185430464</v>
       </c>
       <c r="G16">
-        <v>17.3841059602649</v>
+        <v>18.87417218543046</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>31.14633247327682</v>
+      </c>
+      <c r="C17">
         <v>44.91952328295859</v>
-      </c>
-      <c r="C17">
-        <v>31.14633247327682</v>
       </c>
       <c r="D17">
         <v>2.226203501094092</v>
       </c>
       <c r="E17">
-        <v>25.51290997906489</v>
+        <v>17.69016050244243</v>
       </c>
       <c r="F17">
-        <v>56.79692951849266</v>
+        <v>56.79692951849268</v>
       </c>
       <c r="G17">
-        <v>17.69016050244243</v>
+        <v>25.5129099790649</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.13747464013139</v>
+      </c>
+      <c r="C18">
         <v>45.20336199401024</v>
-      </c>
-      <c r="C18">
-        <v>27.13747464013139</v>
       </c>
       <c r="D18">
         <v>2.212224834366318</v>
       </c>
       <c r="E18">
-        <v>26.22904871349291</v>
+        <v>15.74639834071417</v>
       </c>
       <c r="F18">
         <v>58.02455294579293</v>
       </c>
       <c r="G18">
-        <v>15.74639834071417</v>
+        <v>26.22904871349291</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>27.01906681134708</v>
+      </c>
+      <c r="C19">
         <v>44.50472794915517</v>
-      </c>
-      <c r="C19">
-        <v>27.01906681134708</v>
       </c>
       <c r="D19">
         <v>2.24695228143504</v>
       </c>
       <c r="E19">
-        <v>25.9466787166742</v>
+        <v>15.75237234523272</v>
       </c>
       <c r="F19">
         <v>58.30094893809309</v>
       </c>
       <c r="G19">
-        <v>15.75237234523272</v>
+        <v>25.9466787166742</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>27.27866405448269</v>
+      </c>
+      <c r="C20">
         <v>32.36775818639799</v>
-      </c>
-      <c r="C20">
-        <v>27.27866405448269</v>
       </c>
       <c r="D20">
         <v>3.089494163424125</v>
       </c>
       <c r="E20">
+        <v>17.08692476260044</v>
+      </c>
+      <c r="F20">
+        <v>62.63842220598978</v>
+      </c>
+      <c r="G20">
         <v>20.27465303140979</v>
-      </c>
-      <c r="F20">
-        <v>62.63842220598977</v>
-      </c>
-      <c r="G20">
-        <v>17.08692476260044</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>29.91024175451967</v>
+      </c>
+      <c r="C21">
         <v>34.23514966764046</v>
-      </c>
-      <c r="C21">
-        <v>29.91024175451967</v>
       </c>
       <c r="D21">
         <v>2.920974523868415</v>
       </c>
       <c r="E21">
-        <v>20.85660119423774</v>
+        <v>18.22179806291028</v>
       </c>
       <c r="F21">
         <v>60.92160074285199</v>
       </c>
       <c r="G21">
-        <v>18.22179806291028</v>
+        <v>20.85660119423774</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>31.9977233921457</v>
+      </c>
+      <c r="C22">
         <v>34.83210017074559</v>
-      </c>
-      <c r="C22">
-        <v>31.9977233921457</v>
       </c>
       <c r="D22">
         <v>2.870915032679739</v>
       </c>
       <c r="E22">
-        <v>20.87882096069869</v>
+        <v>19.17985807860262</v>
       </c>
       <c r="F22">
         <v>59.94132096069868</v>
       </c>
       <c r="G22">
-        <v>19.17985807860262</v>
+        <v>20.87882096069869</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.7567281439795</v>
+      </c>
+      <c r="C23">
         <v>36.65793725970914</v>
-      </c>
-      <c r="C23">
-        <v>27.7567281439795</v>
       </c>
       <c r="D23">
         <v>2.727922176622587</v>
       </c>
       <c r="E23">
-        <v>22.29602643395747</v>
+        <v>16.88214860628654</v>
       </c>
       <c r="F23">
         <v>60.82182495975599</v>
       </c>
       <c r="G23">
-        <v>16.88214860628654</v>
+        <v>22.29602643395747</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>27.88311912858049</v>
+      </c>
+      <c r="C24">
         <v>35.42158953374445</v>
-      </c>
-      <c r="C24">
-        <v>27.88311912858049</v>
       </c>
       <c r="D24">
         <v>2.823136999674585</v>
       </c>
       <c r="E24">
-        <v>21.69048879477678</v>
+        <v>17.0742897476619</v>
       </c>
       <c r="F24">
         <v>61.23522145756132</v>
       </c>
       <c r="G24">
-        <v>17.0742897476619</v>
+        <v>21.69048879477678</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>28.08350730688936</v>
+      </c>
+      <c r="C25">
         <v>47.03966597077244</v>
-      </c>
-      <c r="C25">
-        <v>28.08350730688936</v>
       </c>
       <c r="D25">
         <v>2.125865435824605</v>
       </c>
       <c r="E25">
-        <v>26.86090315197177</v>
+        <v>16.03643126221926</v>
       </c>
       <c r="F25">
         <v>57.10266558580898</v>
       </c>
       <c r="G25">
-        <v>16.03643126221926</v>
+        <v>26.86090315197177</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>36.51537884471118</v>
+      </c>
+      <c r="C26">
         <v>34.69617404351088</v>
-      </c>
-      <c r="C26">
-        <v>36.51537884471118</v>
       </c>
       <c r="D26">
         <v>2.882162162162162</v>
       </c>
       <c r="E26">
-        <v>20.26508927593384</v>
+        <v>21.32763720013145</v>
       </c>
       <c r="F26">
         <v>58.40727352393471</v>
       </c>
       <c r="G26">
-        <v>21.32763720013145</v>
+        <v>20.26508927593384</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>31.65236051502146</v>
+      </c>
+      <c r="C27">
         <v>35.08583690987124</v>
-      </c>
-      <c r="C27">
-        <v>31.65236051502146</v>
       </c>
       <c r="D27">
         <v>2.850152905198777</v>
       </c>
       <c r="E27">
-        <v>21.04247104247104</v>
+        <v>18.98326898326899</v>
       </c>
       <c r="F27">
         <v>59.97425997425998</v>
       </c>
       <c r="G27">
-        <v>18.98326898326899</v>
+        <v>21.04247104247104</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>28.71547566856642</v>
+      </c>
+      <c r="C28">
         <v>42.37176676896098</v>
-      </c>
-      <c r="C28">
-        <v>28.71547566856642</v>
       </c>
       <c r="D28">
         <v>2.360062079668908</v>
       </c>
       <c r="E28">
-        <v>24.76617552850736</v>
+        <v>16.78411274823831</v>
       </c>
       <c r="F28">
         <v>58.44971172325432</v>
       </c>
       <c r="G28">
-        <v>16.78411274823831</v>
+        <v>24.76617552850736</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>28.90896455872133</v>
+      </c>
+      <c r="C29">
         <v>40.46212647671994</v>
-      </c>
-      <c r="C29">
-        <v>28.90896455872133</v>
       </c>
       <c r="D29">
         <v>2.471446972949764</v>
       </c>
       <c r="E29">
-        <v>23.88962970561083</v>
+        <v>17.06841727356652</v>
       </c>
       <c r="F29">
         <v>59.04195302082265</v>
       </c>
       <c r="G29">
-        <v>17.06841727356652</v>
+        <v>23.88962970561083</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>27.81740370898716</v>
+      </c>
+      <c r="C30">
         <v>39.59819305753685</v>
-      </c>
-      <c r="C30">
-        <v>27.81740370898716</v>
       </c>
       <c r="D30">
         <v>2.525367757430201</v>
       </c>
       <c r="E30">
+        <v>16.61577788823404</v>
+      </c>
+      <c r="F30">
+        <v>59.73159128026699</v>
+      </c>
+      <c r="G30">
         <v>23.65263083149897</v>
-      </c>
-      <c r="F30">
-        <v>59.73159128026698</v>
-      </c>
-      <c r="G30">
-        <v>16.61577788823404</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>27.25888324873096</v>
+      </c>
+      <c r="C31">
         <v>34.78426395939086</v>
-      </c>
-      <c r="C31">
-        <v>27.25888324873096</v>
       </c>
       <c r="D31">
         <v>2.874863188617293</v>
       </c>
       <c r="E31">
-        <v>21.46605059127575</v>
+        <v>16.82199075886913</v>
       </c>
       <c r="F31">
         <v>61.71195864985511</v>
       </c>
       <c r="G31">
-        <v>16.82199075886913</v>
+        <v>21.46605059127575</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>30.4264374530585</v>
+      </c>
+      <c r="C32">
         <v>45.78152382541935</v>
-      </c>
-      <c r="C32">
-        <v>30.4264374530585</v>
       </c>
       <c r="D32">
         <v>2.184287276704338</v>
       </c>
       <c r="E32">
-        <v>25.9815297182098</v>
+        <v>17.26734548898887</v>
       </c>
       <c r="F32">
         <v>56.75112479280132</v>
       </c>
       <c r="G32">
-        <v>17.26734548898887</v>
+        <v>25.9815297182098</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>28.74187037452344</v>
+      </c>
+      <c r="C33">
         <v>41.31868131868131</v>
-      </c>
-      <c r="C33">
-        <v>28.74187037452344</v>
       </c>
       <c r="D33">
         <v>2.420212765957447</v>
       </c>
       <c r="E33">
-        <v>24.29645259132269</v>
+        <v>16.90096267967823</v>
       </c>
       <c r="F33">
         <v>58.80258472899907</v>
       </c>
       <c r="G33">
-        <v>16.90096267967823</v>
+        <v>24.29645259132269</v>
       </c>
     </row>
   </sheetData>
